--- a/dcf/TOL.xlsx
+++ b/dcf/TOL.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1109,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.07950344829592651</v>
+        <v>0.07923539142893564</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.08450344829592651</v>
+        <v>0.08423539142893564</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.0895034482959265</v>
+        <v>0.08923539142893563</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.09450344829592651</v>
+        <v>0.09423539142893564</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.09950344829592651</v>
+        <v>0.09923539142893564</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.1045034482959265</v>
+        <v>0.1042353914289356</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.1095034482959265</v>
+        <v>0.1092353914289356</v>
       </c>
     </row>
     <row r="5">
@@ -1135,25 +1135,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>221.3638968987123</v>
+        <v>221.8186724757793</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>213.0834707472462</v>
+        <v>213.517818889172</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>205.1737220147924</v>
+        <v>205.5886865195911</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>197.6157633300924</v>
+        <v>198.012329315692</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>190.391766376757</v>
+        <v>190.770863854583</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>183.4848975571665</v>
+        <v>183.8474047721812</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>176.8792578508647</v>
+        <v>177.2260044043268</v>
       </c>
     </row>
     <row r="6">
@@ -1161,25 +1161,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>235.0322736645573</v>
+        <v>235.5210362672562</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>226.1345945285101</v>
+        <v>226.6012450478223</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>217.6381166210912</v>
+        <v>218.0837895397268</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>209.5223133093269</v>
+        <v>209.9480791652562</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>201.7678119605748</v>
+        <v>202.1746812482897</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>194.356323710555</v>
+        <v>194.7452505270326</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>187.270577816408</v>
+        <v>187.6424632695725</v>
       </c>
     </row>
     <row r="7">
@@ -1187,25 +1187,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>248.7006504304024</v>
+        <v>249.2234000587331</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>239.1857183097739</v>
+        <v>239.6846712064725</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>230.1025112273899</v>
+        <v>230.5788925598625</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>221.4288632885614</v>
+        <v>221.8838290148205</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>213.1438575443926</v>
+        <v>213.5784986419965</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>205.2277498639434</v>
+        <v>205.6430962818839</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>197.6618977819512</v>
+        <v>198.0589221348182</v>
       </c>
     </row>
     <row r="8">
@@ -1213,25 +1213,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>262.3690271962475</v>
+        <v>262.9257638502101</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>252.2368420910378</v>
+        <v>252.7680973651227</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>242.5669058336886</v>
+        <v>243.0739955799982</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>233.335413267796</v>
+        <v>233.8195788643848</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>224.5199031282104</v>
+        <v>224.9823160357032</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>216.099176017332</v>
+        <v>216.5409420367353</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>208.0532177474944</v>
+        <v>208.475381000064</v>
       </c>
     </row>
     <row r="9">
@@ -1239,25 +1239,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>276.0374039620926</v>
+        <v>276.6281276416871</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>265.2879658723016</v>
+        <v>265.8515235237729</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>255.0313004399873</v>
+        <v>255.5690986001339</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>245.2419632470305</v>
+        <v>245.7553287139491</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>235.8959487120283</v>
+        <v>236.38613342941</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>226.9706021707205</v>
+        <v>227.4387877915867</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>218.4445377130377</v>
+        <v>218.8918398653097</v>
       </c>
     </row>
     <row r="10">
@@ -1265,25 +1265,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>289.7057807279377</v>
+        <v>290.330491433164</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>278.3390896535655</v>
+        <v>278.9349496824231</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>267.495695046286</v>
+        <v>268.0642016202696</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>257.148513226265</v>
+        <v>257.6910785635133</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>247.2719942958461</v>
+        <v>247.7899508231167</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>237.842028324109</v>
+        <v>238.3366335464381</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>228.8358576785809</v>
+        <v>229.3082987305554</v>
       </c>
     </row>
     <row r="11">
@@ -1291,25 +1291,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>303.3741574937828</v>
+        <v>304.0328552246409</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>291.3902134348294</v>
+        <v>292.0183758410734</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>279.9600896525847</v>
+        <v>280.5593046404053</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>269.0550632054995</v>
+        <v>269.6268284130776</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>258.6480398796639</v>
+        <v>259.1937682168235</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>248.7134544774975</v>
+        <v>249.2344793012895</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>239.2271776441241</v>
+        <v>239.7247575958012</v>
       </c>
     </row>
     <row r="13">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>157.1399993896484</v>
+        <v>152.6600036621094</v>
       </c>
     </row>
     <row r="14">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.09450344829592651</v>
+        <v>0.09423539142893564</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9917392912745795</v>
+        <v>0.9917385223243105</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>157.1399993896484</v>
+        <v>152.6600036621094</v>
       </c>
     </row>
     <row r="49">
@@ -24592,13 +24592,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>233.335413267796</v>
+        <v>233.8195788643848</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>341.3415153510716</v>
+        <v>342.0648087159275</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>155.3459357375079</v>
+        <v>155.6611955324681</v>
       </c>
     </row>
     <row r="59">
